--- a/Downloads/Splitflask-Financials/deliverables/Splitflask_Deal_Workbook.xlsx
+++ b/Downloads/Splitflask-Financials/deliverables/Splitflask_Deal_Workbook.xlsx
@@ -885,7 +885,7 @@
         </is>
       </c>
       <c r="B8" s="15" t="n">
-        <v>106312</v>
+        <v>106411</v>
       </c>
       <c r="C8" s="14" t="n"/>
       <c r="D8" s="15" t="n">
@@ -893,7 +893,7 @@
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>PRELIMINARY ⚠</t>
+          <t>PRELIMINARY ⚠ (intl B2 verified)</t>
         </is>
       </c>
       <c r="F8" s="14" t="inlineStr">
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B9" s="18" t="n">
-        <v>212600</v>
+        <v>212822</v>
       </c>
       <c r="C9" s="17" t="n"/>
       <c r="D9" s="17" t="n"/>
@@ -1623,7 +1623,7 @@
         <v>15940</v>
       </c>
       <c r="D9" s="41" t="n">
-        <v>3000</v>
+        <v>100</v>
       </c>
       <c r="E9" s="39" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="G9" s="32" t="inlineStr">
         <is>
-          <t>2025: Amazon SG/AU $2,383, intl wires $7,686, Best Buy/Walmart $1,111, other. 2026: est.</t>
+          <t>2025: Amazon SG/AU $2,383, intl wires $7,686, Best Buy/Walmart $1,111. 2026 H1: ~$100 actual (SG=$0; AU=$48; MX=$50) — immaterial. Global-e verified inside Shopify export.</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1650,7 @@
         <v>513987</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>109311</v>
+        <v>106411</v>
       </c>
       <c r="E10" s="42" t="n">
         <v>1</v>
@@ -1673,7 +1673,7 @@
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="43" t="inlineStr">
         <is>
-          <t>NARRATIVE: 2025 dip = TRANSITION YEAR (entity restructure SGM→SPLT; TikTok wind-down $155K→$25K). NOT a demand decline — Amazon and Shopify cores held. 2026 re-accelerating post-Shark Tank / Kendra deal; wholesale + intl open items likely additive. The $86K wholesale channel in 2024/2025 has no 2026 data yet.</t>
+          <t>NARRATIVE: 2025 dip = TRANSITION YEAR (entity restructure SGM→SPLT; TikTok wind-down $155K→$25K). NOT a demand decline — Amazon and Shopify cores held. 2026 shows continuing DTC channel normalization: core annualized $184–213K vs 2025 $514K. Honest story = softening DTC; wholesale ($84K/yr) + Best Buy/Walmart + Kendra distribution are the 2026+ growth levers not in run-rate. Global-e confirmed inside Shopify (no add). SG/AU 2026 H1 negligible (~$98 total).</t>
         </is>
       </c>
     </row>
@@ -1887,7 +1887,7 @@
       </c>
       <c r="G9" s="32" t="inlineStr">
         <is>
-          <t>⚠ Global-E intl Shopify pmt $5.4K — may be additive</t>
+          <t>✓ Global-E inside Shopify export (confirmed B2). Not additive.</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1939,7 @@
       <c r="F11" s="6" t="n"/>
       <c r="G11" s="9" t="inlineStr">
         <is>
-          <t>Amazon US + Shopify net + TikTok. Wholesale + Intl + Global-E open (additive).</t>
+          <t>Amazon US + Shopify net + TikTok. ✓ Global-E in Shopify. SG/AU ~$100 (immaterial). Wholesale open.</t>
         </is>
       </c>
     </row>
@@ -2631,7 +2631,7 @@
     <row r="11" ht="48" customHeight="1">
       <c r="A11" s="55" t="inlineStr">
         <is>
-          <t>2026 H1 ~$106K — PRELIMINARY</t>
+          <t>2026 H1 ~$106K — PRELIMINARY (OPEN ITEMS CLOSED B2): Platform-sourced (Amazon Sales Dashboard, Shopify export, TikTok PDFs). NOT held to tax-grade footing. Unaudited. CLOSED: (1) Global-E international — CONFIRMED INSIDE Shopify export; bank math consistent (payout split domestic/intl confirms orders already in dashboard). (2) Amazon SG 2026 = $0 sales. Amazon AU 2026 = A$74.44 ($48 USD, one sale Jan 1). Amazon MX 2026 = MX$907 (~$50 USD). Total intl add = ~$100 — negligible. (3) Atlantic Access = NO CHANGE per owner. REMAINING OPEN: Wholesale 2026 status unconfirmed ($84K channel in 2025).</t>
         </is>
       </c>
       <c r="B11" s="56" t="inlineStr">

--- a/Downloads/Splitflask-Financials/deliverables/Splitflask_Deal_Workbook.xlsx
+++ b/Downloads/Splitflask-Financials/deliverables/Splitflask_Deal_Workbook.xlsx
@@ -885,7 +885,7 @@
         </is>
       </c>
       <c r="B8" s="15" t="n">
-        <v>106411</v>
+        <v>106995</v>
       </c>
       <c r="C8" s="14" t="n"/>
       <c r="D8" s="15" t="n">
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B9" s="18" t="n">
-        <v>212822</v>
+        <v>213990</v>
       </c>
       <c r="C9" s="17" t="n"/>
       <c r="D9" s="17" t="n"/>
@@ -1513,7 +1513,7 @@
         <v>224155</v>
       </c>
       <c r="D5" s="18" t="n">
-        <v>80573</v>
+        <v>81157</v>
       </c>
       <c r="E5" s="39" t="n">
         <v>0.4272574083211529</v>
@@ -1650,7 +1650,7 @@
         <v>513987</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>106411</v>
+        <v>106995</v>
       </c>
       <c r="E10" s="42" t="n">
         <v>1</v>

--- a/Downloads/Splitflask-Financials/deliverables/Splitflask_Deal_Workbook.xlsx
+++ b/Downloads/Splitflask-Financials/deliverables/Splitflask_Deal_Workbook.xlsx
@@ -853,7 +853,7 @@
         </is>
       </c>
       <c r="B7" s="11" t="n">
-        <v>513987</v>
+        <v>517001</v>
       </c>
       <c r="C7" s="12" t="n">
         <v>-0.3162</v>
@@ -1647,7 +1647,7 @@
         <v>751891</v>
       </c>
       <c r="C10" s="7" t="n">
-        <v>513987</v>
+        <v>517001</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>106995</v>
@@ -2078,7 +2078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -2420,88 +2420,108 @@
       </c>
     </row>
     <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="9" t="inlineStr">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Atlantic Access (UK consignment sell-through)</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>3014</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>SPLT</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>INV-8707 (Feb–Aug 2025). £2,336.73 net GMV × 1.29 GBP/USD = $3,014. ~63 units sold at ~£37 avg UK price. PRELIMINARY — exact count + price from AA sales report. Title retained by SPLT per agency contract.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="8" customHeight="1">
+      <c r="A21" s="9" t="inlineStr">
         <is>
           <t>TOTAL 2025</t>
         </is>
       </c>
-      <c r="B20" s="7" t="n">
-        <v>513987</v>
-      </c>
-      <c r="C20" s="6" t="n"/>
-      <c r="D20" s="53" t="n"/>
-      <c r="E20" s="50" t="inlineStr">
+      <c r="B21" s="7" t="n">
+        <v>517001</v>
+      </c>
+      <c r="C21" s="6" t="n"/>
+      <c r="D21" s="53" t="n"/>
+      <c r="E21" s="50" t="inlineStr">
         <is>
           <t>Splitflask tumbler only. Cyberbackpack excluded (separate product, separate entity). Kickstarter $54,386 = deferred revenue (not yet fulfilled Dec 31) — NOT in GMV.</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="8" customHeight="1">
-      <c r="A21" s="3" t="n"/>
-      <c r="B21" s="3" t="n"/>
-      <c r="C21" s="3" t="n"/>
-      <c r="D21" s="3" t="n"/>
-      <c r="E21" s="3" t="n"/>
-      <c r="F21" s="3" t="n"/>
-      <c r="G21" s="3" t="n"/>
-      <c r="H21" s="3" t="n"/>
-    </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="3" t="n"/>
+      <c r="B22" s="3" t="n"/>
+      <c r="C22" s="3" t="n"/>
+      <c r="D22" s="3" t="n"/>
+      <c r="E22" s="3" t="n"/>
+      <c r="F22" s="3" t="n"/>
+      <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>2024 LIST-PRICE DEMAND BRIDGE (the big top-line number)</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="19" t="inlineStr">
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
         <is>
           <t>List-price demand (consumer demand at full price)</t>
         </is>
       </c>
-      <c r="B23" s="18" t="n">
+      <c r="B24" s="18" t="n">
         <v>1032079</v>
       </c>
-      <c r="C23" s="32" t="inlineStr">
+      <c r="C24" s="32" t="inlineStr">
         <is>
           <t>What customers would have paid at list. Larger, legitimate metric.</t>
-        </is>
-      </c>
-      <c r="D23" s="21" t="n"/>
-      <c r="E23" s="22" t="n"/>
-    </row>
-    <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="13" t="inlineStr">
-        <is>
-          <t>Less: Promotional discounts</t>
-        </is>
-      </c>
-      <c r="B24" s="11" t="n">
-        <v>-280188</v>
-      </c>
-      <c r="C24" s="34" t="inlineStr">
-        <is>
-          <t>Promo codes, discount programs. This is a STRENGTH — shows promotional discipline, not weakness.</t>
         </is>
       </c>
       <c r="D24" s="21" t="n"/>
       <c r="E24" s="22" t="n"/>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="9">
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>Less: Promotional discounts</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="n">
+        <v>-280188</v>
+      </c>
+      <c r="C25" s="34" t="inlineStr">
+        <is>
+          <t>Promo codes, discount programs. This is a STRENGTH — shows promotional discipline, not weakness.</t>
+        </is>
+      </c>
+      <c r="D25" s="21" t="n"/>
+      <c r="E25" s="22" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="9">
         <f> GMV (consumer-paid)</f>
         <v/>
       </c>
-      <c r="B25" s="7" t="n">
+      <c r="B26" s="7" t="n">
         <v>751891</v>
       </c>
-      <c r="C25" s="37" t="inlineStr">
+      <c r="C26" s="37" t="inlineStr">
         <is>
           <t>LOCKED. What customers actually paid after promos.</t>
         </is>
       </c>
-      <c r="D25" s="21" t="n"/>
-      <c r="E25" s="22" t="n"/>
+      <c r="D26" s="21" t="n"/>
+      <c r="E26" s="22" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -2524,7 +2544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2595,6 +2615,7 @@
       </c>
       <c r="C6" s="22" t="n"/>
     </row>
+    <row r="7"/>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="54" t="inlineStr">
         <is>
@@ -2654,6 +2675,7 @@
       </c>
       <c r="C12" s="22" t="n"/>
     </row>
+    <row r="13"/>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="54" t="inlineStr">
         <is>
@@ -2700,6 +2722,7 @@
       </c>
       <c r="C17" s="22" t="n"/>
     </row>
+    <row r="18"/>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="54" t="inlineStr">
         <is>
@@ -2785,10 +2808,18 @@
       </c>
       <c r="C25" s="22" t="n"/>
     </row>
+    <row r="26"/>
     <row r="27" ht="36" customHeight="1">
       <c r="A27" s="30" t="inlineStr">
         <is>
           <t>CONFIDENTIAL — Prepared for Kendra Scott / investor due diligence. For information purposes only. Figures represent management's best reconstruction from source documents. 2026 data preliminary and unaudited. This document does not constitute audited financial statements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2025 Atlantic Access sell-through $3,014 | Added 2026-07-11. INV-8707 Feb–Aug 2025. ~63 units net GMV. Cash-basis P&amp;L impact $0 (unpaid invoice). Balance sheet payable $1,769. Increases 2025 GMV $513,987 → $517,001.</t>
         </is>
       </c>
     </row>
